--- a/product_upload/packages/33/file.xlsx
+++ b/product_upload/packages/33/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>ADENURIC 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-903771FFF9B7</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>VITAL E 400 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-7FAC4C8FD8B6</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1208,6 +1223,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>DELAXIN 30 mg delayed-release capsule</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-1C5B85013785</t>
         </is>
       </c>
@@ -1231,7 +1251,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1394,6 +1414,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DELAXIN 60 mg delayed-release capsule</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-C6883F03A7CF</t>
         </is>
       </c>
@@ -1417,7 +1442,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1576,6 +1601,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>PRANZA ODT 5 mg</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-DDEFDFCAC4EC</t>
         </is>
       </c>
@@ -1599,7 +1629,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1758,6 +1788,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>PRANZA ODT 10 mg</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-0462646BF11C</t>
         </is>
       </c>
@@ -1781,7 +1816,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1948,6 +1983,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>PRANZA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-353ADDA10D41</t>
         </is>
       </c>
@@ -1971,7 +2011,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2142,6 +2182,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>PRANZA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-AE753792FF07</t>
         </is>
       </c>
@@ -2165,7 +2210,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2336,6 +2381,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>FYCOMPA 2 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-6B415DB3695D</t>
         </is>
       </c>
@@ -2359,7 +2409,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2522,6 +2572,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>PRIMA D3 5000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-D90B40557F77</t>
         </is>
       </c>
@@ -2545,7 +2600,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2712,6 +2767,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>PRIMA D3 10000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-9A06FCABD455</t>
         </is>
       </c>
@@ -2735,7 +2795,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2898,6 +2958,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>PRIMA D3 50000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-A586B269A6F0</t>
         </is>
       </c>
@@ -2921,7 +2986,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3088,6 +3153,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>NULEX 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-E80FD37F69CD</t>
         </is>
       </c>
@@ -3111,7 +3181,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3270,6 +3340,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>NULEX 300 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-D01F4823DFF5</t>
         </is>
       </c>
@@ -3293,7 +3368,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3448,6 +3523,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>NULEX 400 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-6EC34B3EDED7</t>
         </is>
       </c>
@@ -3471,7 +3551,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3630,6 +3710,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>NULEX 600 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-B6A35695A405</t>
         </is>
       </c>
@@ -3653,7 +3738,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3816,6 +3901,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>NULEX 800 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-AB1A6AC8C22C</t>
         </is>
       </c>
@@ -3839,7 +3929,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4006,6 +4096,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>SEQUIT 25 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-104933AA783A</t>
         </is>
       </c>
@@ -4029,7 +4124,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4196,6 +4291,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>SEQUIT 100 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-B060C1824A47</t>
         </is>
       </c>
@@ -4219,7 +4319,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4390,6 +4490,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>SEQUIT 200 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-FEE3FCDE3370</t>
         </is>
       </c>
@@ -4413,7 +4518,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4580,6 +4685,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>SEQUIT 300 mg Film Coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-EA69B03ADD17</t>
         </is>
       </c>
@@ -4603,7 +4713,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4774,6 +4884,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>AKYNZEO 300 mg/0.5 mg hard capsules</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-3696EBF55620</t>
         </is>
       </c>
@@ -4797,7 +4912,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4960,6 +5075,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>LIXIANA 60 mg film coted tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-07E8136C4A04</t>
         </is>
       </c>
@@ -4983,7 +5103,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5150,6 +5270,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>LIXIANA 30 mg film coted tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-21D3A351CF7E</t>
         </is>
       </c>
@@ -5173,7 +5298,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5332,6 +5457,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>LIXIANA 15 mg film coted tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-A4DF87587BF0</t>
         </is>
       </c>
@@ -5355,7 +5485,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5520,6 +5650,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>VILDATIN 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-5366D149EA23</t>
         </is>
       </c>
@@ -5543,7 +5678,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5712,6 +5847,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>VILDATIN 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-EF2956120D64</t>
         </is>
       </c>
@@ -5735,7 +5875,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5894,6 +6034,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>TEGOZOL 20 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-96D122AB6E3F</t>
         </is>
       </c>
@@ -5917,7 +6062,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6080,6 +6225,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>PRIMA D3 5000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-69600EDE819C</t>
         </is>
       </c>
@@ -6103,7 +6253,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6270,6 +6420,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>PRIMA D3 2000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-B54E791EBED1</t>
         </is>
       </c>
@@ -6293,7 +6448,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6456,6 +6611,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>PRIMA D3 2000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-892E1C0C34D8</t>
         </is>
       </c>
@@ -6479,7 +6639,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6650,6 +6810,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>BETMIGA 25 mg Prolonged Release Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-E35C61090E09</t>
         </is>
       </c>
@@ -6673,7 +6838,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6840,6 +7005,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>BETMIGA 50 mg Prolonged Release Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-9890F2E89D34</t>
         </is>
       </c>
@@ -6863,7 +7033,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7032,6 +7202,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CLOMID 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-8C9DED0E2C76</t>
         </is>
       </c>
@@ -7055,7 +7230,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7210,6 +7385,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>LAGONA 20 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-E1B08F161D42</t>
         </is>
       </c>
@@ -7233,7 +7413,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7388,6 +7568,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>TEGOZOL 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-66FCC1FC4DFD</t>
         </is>
       </c>
@@ -7411,7 +7596,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7570,6 +7755,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>LAGONA 5 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-5F17E63977A1</t>
         </is>
       </c>
@@ -7593,7 +7783,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7756,6 +7946,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>LAGONA 100 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-439456946ACD</t>
         </is>
       </c>
@@ -7779,7 +7974,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7938,6 +8133,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>LAGONA 100 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-5A89FFFF918E</t>
         </is>
       </c>
@@ -7961,7 +8161,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8124,6 +8324,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>LAGONA 5 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-14226966F4B9</t>
         </is>
       </c>
@@ -8147,7 +8352,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8306,6 +8511,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>TEGOZOL 250 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-F9505A99B28D</t>
         </is>
       </c>
@@ -8329,7 +8539,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8500,6 +8710,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>FENSOLIN 5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-0A6C1635FDD7</t>
         </is>
       </c>
@@ -8523,7 +8738,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8694,6 +8909,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>FENSOLIN 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-B4B37882FD9A</t>
         </is>
       </c>
@@ -8717,7 +8937,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8884,6 +9104,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>DEPAKINE 500MG TABS</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-B5BD202BB9D0</t>
         </is>
       </c>
@@ -8907,7 +9132,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9070,6 +9295,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ELOCOM 0.1% LOTION</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-60E2FC871B9C</t>
         </is>
       </c>
@@ -9093,7 +9323,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9268,6 +9498,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>MAVIRET 100 mg/40 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-91BFC4341F6A</t>
         </is>
       </c>
@@ -9291,7 +9526,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9458,6 +9693,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>GLEMAX 1 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-96DE4E78FDBA</t>
         </is>
       </c>
@@ -9481,7 +9721,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9648,6 +9888,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>GLEMAX 2 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-8239494D474C</t>
         </is>
       </c>
@@ -9671,7 +9916,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9834,6 +10079,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>GLEMAX 3 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-B2DB9E706F02</t>
         </is>
       </c>
@@ -9857,7 +10107,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10024,6 +10274,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>GLEMAX 4 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-60BDAD478B05</t>
         </is>
       </c>
@@ -10047,7 +10302,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10210,6 +10465,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>GLEMAX 6 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-6799FA38FD54</t>
         </is>
       </c>
@@ -10233,7 +10493,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10392,6 +10652,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Food)</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-4FCB45AD1651</t>
         </is>
       </c>
@@ -10415,7 +10680,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10578,6 +10843,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Indoor)</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-B83CAECF1D1D</t>
         </is>
       </c>
@@ -10601,7 +10871,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10768,6 +11038,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Mould)</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-34C9F57A8C6A</t>
         </is>
       </c>
@@ -10791,7 +11066,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10954,6 +11229,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Pollen)</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-C8CFC5454E01</t>
         </is>
       </c>
@@ -10977,7 +11257,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11136,6 +11416,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Indoor)</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-116F03952884</t>
         </is>
       </c>
@@ -11159,7 +11444,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11322,6 +11607,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Mould)</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-DF2E37E7A8D7</t>
         </is>
       </c>
@@ -11345,7 +11635,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11512,6 +11802,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>EMANERA 20mg Gastro-Resistant Capsule</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-4D2B8701435A</t>
         </is>
       </c>
@@ -11535,7 +11830,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11698,6 +11993,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>EMANERA 40mg Gastro-Resistant Capsule</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-49A418190891</t>
         </is>
       </c>
@@ -11721,7 +12021,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11884,6 +12184,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>AZYN 500 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-74962BD03E69</t>
         </is>
       </c>
@@ -11907,7 +12212,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12074,6 +12379,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>CERUXIM 250 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-ABF570FF433E</t>
         </is>
       </c>
@@ -12097,7 +12407,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12260,6 +12570,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Pollen)</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-4E0660F7AEE3</t>
         </is>
       </c>
@@ -12283,7 +12598,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12442,6 +12757,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ARBAVASC HCT 160/10/25 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-F3BD155BC48B</t>
         </is>
       </c>
@@ -12465,7 +12785,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12636,6 +12956,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>BUSCOPAN TABLETS 10MG</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-ECD1C99182ED</t>
         </is>
       </c>
@@ -12659,7 +12984,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12818,6 +13143,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>KISQALI 200 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-6F044A33B7FC</t>
         </is>
       </c>
@@ -12841,7 +13171,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13004,6 +13334,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>VULTERA 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-E9D1D7EE288E</t>
         </is>
       </c>
@@ -13027,7 +13362,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13190,6 +13525,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>VULTERA 50 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-9BB660E84857</t>
         </is>
       </c>
@@ -13213,7 +13553,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13376,6 +13716,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>YOCAIR 4 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-1C4C1C56E490</t>
         </is>
       </c>
@@ -13399,7 +13744,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13558,6 +13903,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>YOCAIR 5 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-6D1F0495B1B6</t>
         </is>
       </c>
@@ -13581,7 +13931,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13752,6 +14102,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>SNAFI 5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-308ABE9D1291</t>
         </is>
       </c>
@@ -13775,7 +14130,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13938,6 +14293,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>LORETA 2.5 mg/5 ml Syrup</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-CFA2E3E00FC6</t>
         </is>
       </c>
@@ -13961,7 +14321,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14124,6 +14484,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>LOVERA 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-F4FDB09879C4</t>
         </is>
       </c>
@@ -14147,7 +14512,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14310,6 +14675,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>KISQALI 200 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-806CD4F7B107</t>
         </is>
       </c>
@@ -14333,7 +14703,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14504,6 +14874,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>FUSIDERM 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-164AD4EDE9D5</t>
         </is>
       </c>
@@ -14527,7 +14902,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14702,6 +15077,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>XULTOPHY 100 U/ml + 3.6 mg/ml Solution for  Injection</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-8E5F7530661C</t>
         </is>
       </c>
@@ -14725,7 +15105,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14884,6 +15264,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>EXXARA 8 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-3418A7C1EF8B</t>
         </is>
       </c>
@@ -14907,7 +15292,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15074,6 +15459,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>DIANE-35 TAB</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-F6FCA24D46A2</t>
         </is>
       </c>
@@ -15097,7 +15487,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15264,6 +15654,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>MUCOSOLVAN TAB 30MG</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-B6F116A7E50E</t>
         </is>
       </c>
@@ -15287,7 +15682,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15442,6 +15837,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>KISQALI 200 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-8B4FDC23B515</t>
         </is>
       </c>
@@ -15465,7 +15865,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15624,6 +16024,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>ARBAVASC HCT 160/10/12.5 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-35D7C2D2F7EC</t>
         </is>
       </c>
@@ -15647,7 +16052,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15814,6 +16219,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>ARBAVASC HCT 160/5/25 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-1177A931C87D</t>
         </is>
       </c>
@@ -15837,7 +16247,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16000,6 +16410,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>ARBAVASC HCT 160/5/12.5 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D625B775F85D</t>
         </is>
       </c>
@@ -16023,7 +16438,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16198,6 +16613,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ELEVIT PRONATAL</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-5D0D594BBE3B</t>
         </is>
       </c>
@@ -16221,7 +16641,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16392,6 +16812,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>OLUMIANT 2 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-3F32C80E5513</t>
         </is>
       </c>
@@ -16415,7 +16840,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16582,6 +17007,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>OLUMIANT 2 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-17ACBCCC8737</t>
         </is>
       </c>
@@ -16605,7 +17035,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16780,6 +17210,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>OLUMIANT 4 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-A8885FACBBA1</t>
         </is>
       </c>
@@ -16803,7 +17238,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16966,6 +17401,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>OLUMIANT 4 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-623A1E054FBE</t>
         </is>
       </c>
@@ -16989,7 +17429,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17144,6 +17584,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>MEXIA 10 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-36D36958985C</t>
         </is>
       </c>
@@ -17167,7 +17612,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17330,6 +17775,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>OLMEPRESS 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-40EE5694F335</t>
         </is>
       </c>
@@ -17353,7 +17803,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17520,6 +17970,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>ADEMPAS 0.5 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-0AEE22D4CDC8</t>
         </is>
       </c>
@@ -17543,7 +17998,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17710,6 +18165,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>ADEMPAS 1 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-9E9500823CC8</t>
         </is>
       </c>
@@ -17733,7 +18193,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17900,6 +18360,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>ADEMPAS 1.5 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-FFFCBD2BB647</t>
         </is>
       </c>
@@ -17923,7 +18388,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18082,6 +18547,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>ADEMPAS 2 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-FD6F71DBA1D5</t>
         </is>
       </c>
@@ -18105,7 +18575,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18272,6 +18742,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>ADEMPAS 2.5 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-CC774ACE851C</t>
         </is>
       </c>
@@ -18295,7 +18770,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18462,6 +18937,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>ORGALUTRAN 0.25MG\0.5ML SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-62A03C8907B1</t>
         </is>
       </c>
@@ -18485,7 +18965,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18652,6 +19132,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>PROVERA 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-DD9BB8B2CC64</t>
         </is>
       </c>
@@ -18675,7 +19160,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18842,6 +19327,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>DEPAKINE 200MG TABS</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-0659DC72AB23</t>
         </is>
       </c>
@@ -18865,7 +19355,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19024,6 +19514,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>OLMEPRESS 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-8355B2F0AA04</t>
         </is>
       </c>
@@ -19047,7 +19542,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19210,6 +19705,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>AMEP 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-F3E581517638</t>
         </is>
       </c>
@@ -19233,7 +19733,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19403,6 +19903,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>ELONVA 150 mcg Solution For Injection</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-6A4943153CF9</t>
         </is>
@@ -19419,7 +19924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19465,100 +19970,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19590,7 +20100,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19605,92 +20115,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-99252</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>222.15</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>275</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19722,7 +20237,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19737,92 +20252,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-30824</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>204.81</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>276</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19854,7 +20374,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19869,92 +20389,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-58443</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>63.78</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>277</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19986,7 +20511,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20001,92 +20526,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-42022</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>82.77</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>278</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20118,7 +20648,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20133,92 +20663,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-77273</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>140.1</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>279</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20250,7 +20785,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20265,92 +20800,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-31567</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>411.18</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>280</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20382,7 +20922,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20397,92 +20937,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-21225</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>467.72</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>281</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20514,7 +21059,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20529,92 +21074,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-14538</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>35.05</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>282</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20646,7 +21196,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20661,92 +21211,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-17005</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>136.36</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>283</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20778,7 +21333,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20793,92 +21348,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-55491</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>128.07</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>284</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20910,7 +21470,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20925,92 +21485,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-82733</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>330.39</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>285</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21027,7 +21592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21133,6 +21698,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21168,7 +21743,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21233,6 +21808,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-589EBAC7109B</t>
         </is>
@@ -21269,7 +21854,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21334,6 +21919,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-2BD6FE0850A4</t>
         </is>
@@ -21370,7 +21965,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21435,6 +22030,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-F6403E35453C</t>
         </is>
@@ -21471,7 +22076,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21536,6 +22141,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-2B8A8B68F2D1</t>
         </is>
@@ -21572,7 +22187,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21637,6 +22252,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-DF6FAFF3B9F0</t>
         </is>
@@ -21673,7 +22298,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21738,6 +22363,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-740B92536755</t>
         </is>
@@ -21774,7 +22409,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21839,6 +22474,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-67F84F0F50CB</t>
         </is>
@@ -21875,7 +22520,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21940,6 +22585,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-B5B2699D4A2E</t>
         </is>
@@ -21976,7 +22631,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22041,6 +22696,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-70D872BF34C5</t>
         </is>
@@ -22077,7 +22742,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22142,6 +22807,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-DC25A93633A9</t>
         </is>
@@ -22178,7 +22853,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22243,6 +22918,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-39FC373482E3</t>
         </is>
@@ -22279,7 +22964,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22344,6 +23029,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-0D8354DA6119</t>
         </is>
@@ -22380,7 +23075,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22445,6 +23140,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-D153295640B2</t>
         </is>
@@ -22481,7 +23186,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22546,6 +23251,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-08C3AAB4849C</t>
         </is>
@@ -22582,7 +23297,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22647,6 +23362,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-6B6E50DAFBC5</t>
         </is>
@@ -22683,7 +23408,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22748,6 +23473,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-26FF214C06CF</t>
         </is>
@@ -22784,7 +23519,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22849,6 +23584,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-0D0DFED62158</t>
         </is>
@@ -22885,7 +23630,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22950,6 +23695,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-05C499C1955C</t>
         </is>
@@ -22986,7 +23741,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23051,6 +23806,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-7B6637450BCA</t>
         </is>
@@ -23087,7 +23852,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23152,6 +23917,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-B52937BDFC96</t>
         </is>

--- a/product_upload/packages/33/file.xlsx
+++ b/product_upload/packages/33/file.xlsx
@@ -686,8 +686,16 @@
           <t>8120581115-341-570730589144</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADENURIC 80 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ADENURIC 80 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1072,8 +1080,16 @@
           <t>7060238221-948-241715767562</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DELAXIN 30 mg delayed-release capsule</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DELAXIN 30 mg delayed-release capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1259,8 +1275,16 @@
           <t>5090195563-456-719296611397</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DELAXIN 60 mg delayed-release capsule</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DELAXIN 60 mg delayed-release capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1450,8 +1474,16 @@
           <t>8267357505-971-215483389318</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRANZA ODT 5 mg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PRANZA ODT 5 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1637,8 +1669,16 @@
           <t>3884498320-285-529559458320</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRANZA ODT 10 mg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PRANZA ODT 10 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -3189,8 +3229,16 @@
           <t>2251467839-719-938618396305</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NULEX 300 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NULEX 300 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3376,8 +3424,16 @@
           <t>1491771058-620-057279457879</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NULEX 400 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NULEX 400 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3559,8 +3615,16 @@
           <t>9365692052-642-687342589826</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NULEX 600 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NULEX 600 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3746,8 +3810,16 @@
           <t>3217090956-599-264016474336</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NULEX 800 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NULEX 800 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -5306,8 +5378,16 @@
           <t>2966576300-484-299850456971</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIXIANA 15 mg film coted tablet</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>LIXIANA 15 mg film coted tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5493,8 +5573,16 @@
           <t>5154095837-813-719720324093</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VILDATIN 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VILDATIN 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -5686,8 +5774,16 @@
           <t>7363013888-828-521415928489</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VILDATIN 50 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VILDATIN 50 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -5883,8 +5979,16 @@
           <t>6420544404-631-736069079268</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TEGOZOL 20 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TEGOZOL 20 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6070,8 +6174,16 @@
           <t>1724244407-452-683169927782</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRIMA D3 5000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PRIMA D3 5000 IU softgel capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6456,8 +6568,16 @@
           <t>5287850074-789-081362675270</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRIMA D3 2000 IU softgel capsule</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PRIMA D3 2000 IU softgel capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -7238,8 +7358,16 @@
           <t>8335693977-983-540646234000</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAGONA 20 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>LAGONA 20 mg  Hard capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7421,8 +7549,16 @@
           <t>9078821969-934-016561160200</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TEGOZOL 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TEGOZOL 100 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7604,8 +7740,16 @@
           <t>1908104445-908-327937690202</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAGONA 5 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>LAGONA 5 mg  Hard capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7791,8 +7935,16 @@
           <t>7288616758-600-344324051752</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAGONA 100 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>LAGONA 100 mg  Hard capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7982,8 +8134,16 @@
           <t>0045363615-904-358064365388</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAGONA 100 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>LAGONA 100 mg  Hard capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8169,8 +8329,16 @@
           <t>3895642437-381-087456167742</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAGONA 5 mg  Hard capsule</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>LAGONA 5 mg  Hard capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8360,8 +8528,16 @@
           <t>4443646451-990-169478891452</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TEGOZOL 250 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TEGOZOL 250 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -9140,8 +9316,16 @@
           <t>3312652080-739-503725573508</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELOCOM 0.1% LOTION</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ELOCOM 0.1% LOTION detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9534,8 +9718,16 @@
           <t>7359020055-307-379623621635</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLEMAX 1 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>GLEMAX 1 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9729,8 +9921,16 @@
           <t>7307262018-871-640755730562</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLEMAX 2 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>GLEMAX 2 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9924,8 +10124,16 @@
           <t>3281693614-692-770401801028</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLEMAX 3 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>GLEMAX 3 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10115,8 +10323,16 @@
           <t>6001420778-775-391005302908</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLEMAX 4 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>GLEMAX 4 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10310,8 +10526,16 @@
           <t>7236779830-896-824957789767</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLEMAX 6 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>GLEMAX 6 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10501,8 +10725,16 @@
           <t>3608982294-807-847831000079</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRIC-TEK Sol. for Skin Prick Test (Food)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Food) detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10688,8 +10920,16 @@
           <t>0951645045-184-244119575089</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRIC-TEK Sol. for Skin Prick Test (Indoor)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Indoor) detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10879,8 +11119,16 @@
           <t>1194938560-586-899105369477</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRIC-TEK Sol. for Skin Prick Test (Mould)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Mould) detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11074,8 +11322,16 @@
           <t>9264722307-662-746155984068</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Pollen)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Pollen) detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11265,8 +11521,16 @@
           <t>1922472168-084-888776865790</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Indoor)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Indoor) detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11452,8 +11716,16 @@
           <t>7742784645-406-844640073387</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Mould)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ALLERGOTEK Oraltek 30.000 TU/ml Sol. for Sublingual Spray (Mould) detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11838,8 +12110,16 @@
           <t>0599823813-073-738797907659</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMANERA 40mg Gastro-Resistant Capsule</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>EMANERA 40mg Gastro-Resistant Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12029,8 +12309,16 @@
           <t>1501785564-791-057594915773</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AZYN 500 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>AZYN 500 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12220,8 +12508,16 @@
           <t>8730916852-448-136026990207</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CERUXIM 250 mg Film Coted Tablet</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CERUXIM 250 mg Film Coted Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12415,8 +12711,16 @@
           <t>2545541053-992-524585844437</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PRIC-TEK Sol. for Skin Prick Test (Pollen)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PRIC-TEK Sol. for Skin Prick Test (Pollen) detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12606,8 +12910,16 @@
           <t>8618314431-933-123256281146</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVASC HCT 160/10/25 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ARBAVASC HCT 160/10/25 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12992,8 +13304,16 @@
           <t>6941618983-115-542896319998</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KISQALI 200 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>KISQALI 200 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13179,8 +13499,16 @@
           <t>9816539512-245-497340433770</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VULTERA 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>VULTERA 200 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13370,8 +13698,16 @@
           <t>3002023748-580-191728391165</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VULTERA 50 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>VULTERA 50 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13561,8 +13897,16 @@
           <t>6788254924-241-136494125791</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ YOCAIR 4 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>YOCAIR 4 mg Chewable Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13752,8 +14096,16 @@
           <t>5131526726-088-091866063466</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ YOCAIR 5 mg Chewable Tablets</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>YOCAIR 5 mg Chewable Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14138,8 +14490,16 @@
           <t>2374063126-729-563253222197</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LORETA 2.5 mg/5 ml Syrup</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LORETA 2.5 mg/5 ml Syrup detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14329,8 +14689,16 @@
           <t>7355258239-068-292169218710</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOVERA 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LOVERA 10 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -15113,8 +15481,16 @@
           <t>1994015367-718-806474862781</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EXXARA 8 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>EXXARA 8 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15690,8 +16066,16 @@
           <t>8965106798-223-121353991271</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KISQALI 200 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>KISQALI 200 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15873,8 +16257,16 @@
           <t>3157143529-255-311697953665</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVASC HCT 160/10/12.5 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ARBAVASC HCT 160/10/12.5 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16060,8 +16452,16 @@
           <t>5249422064-926-764800143106</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVASC HCT 160/5/25 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>ARBAVASC HCT 160/5/25 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16255,8 +16655,16 @@
           <t>8954407569-990-351457714616</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBAVASC HCT 160/5/12.5 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ARBAVASC HCT 160/5/12.5 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16848,8 +17256,16 @@
           <t>1362575560-570-970949317148</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLUMIANT 2 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>OLUMIANT 2 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17246,8 +17662,16 @@
           <t>9005161412-881-169616862620</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLUMIANT 4 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OLUMIANT 4 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17437,8 +17861,16 @@
           <t>2549065682-347-652837629774</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MEXIA 10 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MEXIA 10 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17620,8 +18052,16 @@
           <t>4148311038-517-602467470314</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMEPRESS 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>OLMEPRESS 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17811,8 +18251,16 @@
           <t>6343399586-851-536941999542</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADEMPAS 0.5 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ADEMPAS 0.5 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18006,8 +18454,16 @@
           <t>1185578752-957-357833054422</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADEMPAS 1 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ADEMPAS 1 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18201,8 +18657,16 @@
           <t>1463659468-149-600908448873</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADEMPAS 1.5 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>ADEMPAS 1.5 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18396,8 +18860,16 @@
           <t>5258215985-077-736209354719</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADEMPAS 2 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ADEMPAS 2 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18583,8 +19055,16 @@
           <t>9559320698-718-294935592510</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADEMPAS 2.5 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ADEMPAS 2.5 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19363,8 +19843,16 @@
           <t>4126026943-348-966641445733</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMEPRESS 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>OLMEPRESS 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19550,8 +20038,16 @@
           <t>8699971584-453-577125169601</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMEP 10 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>AMEP 10 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/33/file.xlsx
+++ b/product_upload/packages/33/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22088,7 +22088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22169,40 +22169,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22282,38 +22287,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>334.43</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-589EBAC7109B</t>
         </is>
@@ -22393,38 +22403,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>87.31999999999999</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-2BD6FE0850A4</t>
         </is>
@@ -22504,38 +22519,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>410.74</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-F6403E35453C</t>
         </is>
@@ -22615,38 +22635,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>265.39</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-2B8A8B68F2D1</t>
         </is>
@@ -22726,38 +22751,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>355.3</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-DF6FAFF3B9F0</t>
         </is>
@@ -22837,38 +22867,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>218.32</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-740B92536755</t>
         </is>
@@ -22948,38 +22983,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>437.22</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-67F84F0F50CB</t>
         </is>
@@ -23059,38 +23099,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>115.32</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-B5B2699D4A2E</t>
         </is>
@@ -23170,38 +23215,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>269.58</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-70D872BF34C5</t>
         </is>
@@ -23281,38 +23331,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>160.8</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-DC25A93633A9</t>
         </is>
@@ -23392,38 +23447,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>317.1</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-39FC373482E3</t>
         </is>
@@ -23503,38 +23563,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>110.38</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-0D8354DA6119</t>
         </is>
@@ -23614,38 +23679,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>406.33</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-D153295640B2</t>
         </is>
@@ -23725,38 +23795,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>55.59</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-08C3AAB4849C</t>
         </is>
@@ -23836,38 +23911,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>24.18</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-6B6E50DAFBC5</t>
         </is>
@@ -23947,38 +24027,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>40.31</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-26FF214C06CF</t>
         </is>
@@ -24058,38 +24143,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>231.7</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-0D0DFED62158</t>
         </is>
@@ -24169,38 +24259,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>88.55</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-05C499C1955C</t>
         </is>
@@ -24280,38 +24375,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>286.44</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-7B6637450BCA</t>
         </is>
@@ -24391,38 +24491,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>372.84</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-B52937BDFC96</t>
         </is>
